--- a/EngineMap.xlsx
+++ b/EngineMap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Christos\Desktop\VDSE v 1.1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HAWKS\Documents\VPE Projekt\Projektarbeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D6A8BD-8950-4A64-98B3-0DADF328CC98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607D78B5-0627-4EF9-A35F-D5D0614CECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4836" yWindow="2064" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,20 +38,26 @@
     <t>RPM</t>
   </si>
   <si>
-    <t>z = 0</t>
+    <t>Torque</t>
   </si>
   <si>
-    <t>z = 1</t>
+    <t>Throttle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -81,7 +87,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -359,198 +365,231 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B2">
-        <f>(0*( 1/1000))/3</f>
         <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>50</v>
+      </c>
+      <c r="B3">
         <v>500</v>
       </c>
-      <c r="B3">
-        <v>-9.6229999999999993</v>
-      </c>
       <c r="C3">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5.5555555E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
+        <v>50</v>
+      </c>
+      <c r="B4">
         <v>1000</v>
       </c>
-      <c r="B4">
-        <v>-26.777999999999999</v>
-      </c>
       <c r="C4">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.11111111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>50</v>
+      </c>
+      <c r="B5">
         <v>1600</v>
       </c>
-      <c r="B5">
-        <v>-34.427999999999997</v>
-      </c>
       <c r="C5">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.16666666499999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
+        <v>50</v>
+      </c>
+      <c r="B6">
         <v>2000</v>
       </c>
-      <c r="B6">
-        <v>-38.253999999999998</v>
-      </c>
       <c r="C6">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.22222222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
+        <v>50</v>
+      </c>
+      <c r="B7">
         <v>3000</v>
       </c>
-      <c r="B7">
-        <v>-72.921000000000006</v>
-      </c>
       <c r="C7">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.277777775</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>50</v>
+      </c>
+      <c r="B8">
         <v>4000</v>
       </c>
-      <c r="B8">
-        <v>-96.033000000000001</v>
-      </c>
       <c r="C8">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.33333332999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
+        <v>50</v>
+      </c>
+      <c r="B9">
         <v>4300</v>
       </c>
-      <c r="B9">
-        <v>-100</v>
-      </c>
       <c r="C9">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.38888888500000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
+        <v>50</v>
+      </c>
+      <c r="B10">
         <v>4500</v>
       </c>
-      <c r="B10">
-        <v>-107.59</v>
-      </c>
       <c r="C10">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.44444444</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
         <v>5000</v>
       </c>
-      <c r="B11">
-        <v>-118.35</v>
-      </c>
       <c r="C11">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.49999999499999997</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
+        <v>50</v>
+      </c>
+      <c r="B12">
         <v>5400</v>
       </c>
-      <c r="B12">
-        <v>-130</v>
-      </c>
       <c r="C12">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.55555555000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
+        <v>50</v>
+      </c>
+      <c r="B13">
         <v>5900</v>
       </c>
-      <c r="B13">
-        <v>-180</v>
-      </c>
       <c r="C13">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.61111110499999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
+        <v>50</v>
+      </c>
+      <c r="B14">
         <v>6000</v>
       </c>
-      <c r="B14">
-        <v>-190</v>
-      </c>
       <c r="C14">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.66666665999999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
+        <v>50</v>
+      </c>
+      <c r="B15">
         <v>6400</v>
       </c>
-      <c r="B15">
-        <v>-200</v>
-      </c>
       <c r="C15">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.72222221499999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
+        <v>47</v>
+      </c>
+      <c r="B16">
         <v>6700</v>
       </c>
-      <c r="B16">
-        <v>-210</v>
-      </c>
       <c r="C16">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.77777777000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
+        <v>44</v>
+      </c>
+      <c r="B17">
         <v>7000</v>
       </c>
-      <c r="B17">
-        <v>-230</v>
-      </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.83333332500000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>41</v>
+      </c>
+      <c r="B18">
+        <v>7350</v>
+      </c>
+      <c r="C18">
+        <v>0.88888887999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>38</v>
+      </c>
+      <c r="B19">
+        <v>7680</v>
+      </c>
+      <c r="C19">
+        <v>0.94444443499999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>8010</v>
+      </c>
+      <c r="C20">
+        <v>0.99999998999999995</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>